--- a/GRC_Dashboard.xlsx
+++ b/GRC_Dashboard.xlsx
@@ -1,38 +1,137 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\65881\Downloads\GRC Project\GRC-Project\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D16ECDE-0AA1-4DB5-AA28-154A7ADAACA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" r:id="rId2"/>
+    <sheet name="Dashboard" sheetId="2" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="13" r:id="rId4"/>
+  </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+  <si>
+    <t>Risk_ID</t>
+  </si>
+  <si>
+    <t>Risk</t>
+  </si>
+  <si>
+    <t>Impact</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Covered</t>
+  </si>
+  <si>
+    <t>R001</t>
+  </si>
+  <si>
+    <t>Money laundering</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Transaction Monitoring</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>R002</t>
+  </si>
+  <si>
+    <t>Data breach</t>
+  </si>
+  <si>
+    <t>Access Control</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>R003</t>
+  </si>
+  <si>
+    <t>Fraud</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Fraud Detection</t>
+  </si>
+  <si>
+    <t>GRC Dashboard</t>
+  </si>
+  <si>
+    <t>Total Risks</t>
+  </si>
+  <si>
+    <t>Covered Risks</t>
+  </si>
+  <si>
+    <t>Uncovered Risks</t>
+  </si>
+  <si>
+    <t>Count of Risk_ID</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -47,82 +146,1594 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="105"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="5"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[GRC_Dashboard.xlsx]Sheet1!PivotTable7</c:name>
+    <c:fmtId val="12"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-SG"/>
+              <a:t>Count of Risk_ID by Impact</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="9BBB59">
+                <a:alpha val="70000"/>
+              </a:srgbClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="9BBB59">
+                <a:alpha val="70000"/>
+              </a:srgbClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:xForSave val="1"/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="9BBB59">
+                <a:alpha val="70000"/>
+              </a:srgbClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:xForSave val="1"/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-809A-49AB-9488-FCA3BC83B76D}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-809A-49AB-9488-FCA3BC83B76D}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="9BBB59">
+                    <a:alpha val="70000"/>
+                  </a:srgbClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-809A-49AB-9488-FCA3BC83B76D}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="9BBB59">
+                    <a:alpha val="70000"/>
+                  </a:srgbClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-809A-49AB-9488-FCA3BC83B76D}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="9BBB59">
+                  <a:alpha val="70000"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent3">
+                          <a:lumMod val="60000"/>
+                          <a:lumOff val="40000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$4:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>No</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Yes</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$4:$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-809A-49AB-9488-FCA3BC83B76D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="269"/>
+        <c:overlap val="-20"/>
+        <c:axId val="1058666255"/>
+        <c:axId val="1058672015"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1058666255"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:alpha val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1058672015"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1058672015"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1058666255"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="accent3"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="accent3"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="16">
+  <a:schemeClr val="accent3"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="214">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="800" kern="1200" cap="all" spc="150" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="70000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:styleClr val="auto"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst>
+        <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
+          <a:schemeClr val="phClr"/>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="22225">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="35000"/>
+          <a:lumOff val="65000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="25400">
+          <a:schemeClr val="lt1"/>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+            <a:tint val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1500" b="1" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E0373BC-0862-4303-BC6A-6377627F1122}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Kathuri Gunasekara Alwar" refreshedDate="46119.393516319447" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{00898E19-6073-4D37-B8A1-3E4B7C97AAA3}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:E4" sheet="Data"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="Risk_ID" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Risk" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Impact" numFmtId="0">
+      <sharedItems count="2">
+        <s v="High"/>
+        <s v="Medium"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Control" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Transaction Monitoring"/>
+        <s v="Access Control"/>
+        <s v="Fraud Detection"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Covered" numFmtId="0">
+      <sharedItems count="2">
+        <s v="Yes"/>
+        <s v="No"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="3">
+  <r>
+    <s v="R001"/>
+    <s v="Money laundering"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="R002"/>
+    <s v="Data breach"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="R003"/>
+    <s v="Fraud"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1A8247FE-5C11-450E-B3EA-29D1564D9EDD}" name="PivotTable7" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="17">
+  <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="2">
+        <item x="0"/>
+        <item x="1"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="2">
+        <item x="1"/>
+        <item x="0"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Risk_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="11">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="5">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" fillDownLabelsDefault="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -409,177 +2020,195 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FAFABDF-BF5F-4D08-9E9B-152F6E0CB7CE}">
+  <dimension ref="A3:B5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="14.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Risk_ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Risk</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Covered</t>
-        </is>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>R001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Money laundering</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Transaction Monitoring</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>R002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Data breach</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Access Control</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>R003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Fraud Detection</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D11">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3">
+    <cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",A3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="No">
+      <formula>NOT(ISERROR(SEARCH("No",A3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="No">
+      <formula>NOT(ISERROR(SEARCH("No",A1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>GRC Dashboard</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Total Risks</t>
-        </is>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>19</v>
       </c>
       <c r="B3">
         <f>COUNTA(Data!A2:A100)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Covered Risks</t>
-        </is>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>20</v>
       </c>
       <c r="B4">
         <f>COUNTIF(Data!E2:E100,"Yes")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Uncovered Risks</t>
-        </is>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>21</v>
       </c>
       <c r="B5">
         <f>COUNTIF(Data!E2:E100,"No")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="O5">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",O5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>